--- a/__履歴__/スコアの観点.xlsx
+++ b/__履歴__/スコアの観点.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BizOwn\000_Biw2\51_googleantigravity\007_kaggle_Biohub-Cell_Tracking_During_Development\s3_results_integration_and_submission\__履歴__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7792ECE-3372-41DD-BC8F-5F65703C3A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B56BA0-91BA-4D1C-8728-227DCD5F0569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22284" yWindow="4836" windowWidth="21912" windowHeight="19632" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11760" yWindow="3180" windowWidth="21912" windowHeight="19632" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>s3_100_results_integration_and_submission.ipynb</t>
   </si>
@@ -183,6 +183,10 @@
     <rPh sb="3" eb="5">
       <t>ザンテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D: p32x64x64_sig1.5x1.0_lr0.001</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -220,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -426,11 +430,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -499,6 +529,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -779,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="19.296875" customWidth="1"/>
@@ -1114,7 +1156,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:13">
       <c r="B17" s="10" t="s">
         <v>10</v>
       </c>
@@ -1149,83 +1191,271 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B18" s="12" t="s">
+    <row r="18" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="4">
         <v>6335</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="4">
         <v>8463</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="5">
         <v>1033</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="4">
         <v>5302</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="5">
         <v>165</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="4">
         <v>0.16309999999999999</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="5">
         <v>0.86229999999999996</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="29">
         <v>0.27429999999999999</v>
       </c>
       <c r="L18" s="20">
         <v>46271</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="16" t="s">
+    <row r="19" spans="2:13">
+      <c r="B19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="8">
+        <v>19506</v>
+      </c>
+      <c r="E19" s="8">
+        <v>25755</v>
+      </c>
+      <c r="F19" s="7">
+        <v>49</v>
+      </c>
+      <c r="G19" s="8">
+        <v>19457</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3</v>
+      </c>
+      <c r="I19" s="8">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0.94230000000000003</v>
+      </c>
+      <c r="K19" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="20"/>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3197</v>
+      </c>
+      <c r="E20" s="2">
+        <v>32795</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3196</v>
+      </c>
+      <c r="H20" s="3">
+        <v>50</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="K20" s="11">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="L20" s="26"/>
+      <c r="M20" s="20"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2684</v>
+      </c>
+      <c r="E21" s="2">
+        <v>15090</v>
+      </c>
+      <c r="F21" s="3">
+        <v>36</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2648</v>
+      </c>
+      <c r="H21" s="3">
+        <v>104</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1.34E-2</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.2571</v>
+      </c>
+      <c r="K21" s="11">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="L21" s="26"/>
+      <c r="M21" s="20"/>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4482</v>
+      </c>
+      <c r="E22" s="2">
+        <v>6362</v>
+      </c>
+      <c r="F22" s="3">
+        <v>758</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3724</v>
+      </c>
+      <c r="H22" s="3">
+        <v>103</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.1691</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.88039999999999996</v>
+      </c>
+      <c r="K22" s="11">
+        <v>0.28370000000000001</v>
+      </c>
+      <c r="L22" s="26"/>
+      <c r="M22" s="20"/>
+    </row>
+    <row r="23" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B23" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="14">
+        <v>6559</v>
+      </c>
+      <c r="E23" s="14">
+        <v>8463</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1068</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5491</v>
+      </c>
+      <c r="H23" s="13">
+        <v>130</v>
+      </c>
+      <c r="I23" s="14">
+        <v>0.1628</v>
+      </c>
+      <c r="J23" s="13">
+        <v>0.89149999999999996</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0.27539999999999998</v>
+      </c>
+      <c r="L23" s="26"/>
+      <c r="M23" s="20"/>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D20">
+      <c r="D26">
         <v>7981.3</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E26" s="16">
         <v>97.7</v>
       </c>
-      <c r="F20" s="18">
-        <f>D20-E20</f>
+      <c r="F26" s="18">
+        <f>D26-E26</f>
         <v>7883.6</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G26" t="s">
         <v>22</v>
       </c>
-      <c r="H20">
-        <f>F20/3600/4</f>
+      <c r="H26">
+        <f>F26/3600/4</f>
         <v>0.54747222222222225</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
-      <c r="C21" s="2" t="s">
+    <row r="27" spans="2:13">
+      <c r="C27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D21">
+      <c r="D27">
         <v>10053</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="16">
+      <c r="E27" s="18"/>
+      <c r="F27" s="16">
         <v>10053</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G27" t="s">
         <v>24</v>
       </c>
-      <c r="H21">
-        <f>F21/3600/4</f>
+      <c r="H27">
+        <f>F27/3600/4</f>
         <v>0.698125</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="C28" s="16" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/__履歴__/スコアの観点.xlsx
+++ b/__履歴__/スコアの観点.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BizOwn\000_Biw2\51_googleantigravity\007_kaggle_Biohub-Cell_Tracking_During_Development\s3_results_integration_and_submission\__履歴__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B56BA0-91BA-4D1C-8728-227DCD5F0569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C8EB65-28E9-4F67-8177-4B84960A6C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11760" yWindow="3180" windowWidth="21912" windowHeight="19632" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1082,8 +1082,8 @@
       <c r="K14" s="24">
         <v>0.28470000000000001</v>
       </c>
-      <c r="L14" s="19">
-        <v>46269</v>
+      <c r="L14" s="20">
+        <v>46270</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1257,7 +1257,9 @@
       <c r="K19" s="9">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="L19" s="26"/>
+      <c r="L19" s="20">
+        <v>46271</v>
+      </c>
       <c r="M19" s="20"/>
     </row>
     <row r="20" spans="2:13">
@@ -1291,7 +1293,9 @@
       <c r="K20" s="11">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="L20" s="26"/>
+      <c r="L20" s="20">
+        <v>46271</v>
+      </c>
       <c r="M20" s="20"/>
     </row>
     <row r="21" spans="2:13">
@@ -1325,7 +1329,9 @@
       <c r="K21" s="11">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="L21" s="26"/>
+      <c r="L21" s="20">
+        <v>46271</v>
+      </c>
       <c r="M21" s="20"/>
     </row>
     <row r="22" spans="2:13">
@@ -1359,7 +1365,9 @@
       <c r="K22" s="11">
         <v>0.28370000000000001</v>
       </c>
-      <c r="L22" s="26"/>
+      <c r="L22" s="20">
+        <v>46271</v>
+      </c>
       <c r="M22" s="20"/>
     </row>
     <row r="23" spans="2:13" ht="18.600000000000001" thickBot="1">
@@ -1393,7 +1401,9 @@
       <c r="K23" s="15">
         <v>0.27539999999999998</v>
       </c>
-      <c r="L23" s="26"/>
+      <c r="L23" s="20">
+        <v>46271</v>
+      </c>
       <c r="M23" s="20"/>
     </row>
     <row r="24" spans="2:13">

--- a/__履歴__/スコアの観点.xlsx
+++ b/__履歴__/スコアの観点.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BizOwn\000_Biw2\51_googleantigravity\007_kaggle_Biohub-Cell_Tracking_During_Development\s3_results_integration_and_submission\__履歴__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C8EB65-28E9-4F67-8177-4B84960A6C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E880E8-72AF-4229-846D-E9DD9123F5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="3180" windowWidth="21912" windowHeight="19632" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20832" yWindow="4164" windowWidth="21912" windowHeight="19632" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="89">
   <si>
     <t>s3_100_results_integration_and_submission.ipynb</t>
   </si>
@@ -189,12 +189,222 @@
     <t>D: p32x64x64_sig1.5x1.0_lr0.001</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Blob Dog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データセット</t>
+  </si>
+  <si>
+    <r>
+      <t>閾値 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF101010"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>検出数 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Pred</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF101010"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>GT推定総数</t>
+  </si>
+  <si>
+    <t>推定比</t>
+  </si>
+  <si>
+    <t>Recall（再現率）</t>
+  </si>
+  <si>
+    <t>適合率 (Prec)</t>
+  </si>
+  <si>
+    <t>F1-Score</t>
+  </si>
+  <si>
+    <t>平均誤差距離</t>
+  </si>
+  <si>
+    <t>処理時間</t>
+  </si>
+  <si>
+    <t>(GT検証: 51)</t>
+  </si>
+  <si>
+    <t>0.0000 (0/51)</t>
+  </si>
+  <si>
+    <t>0.2353 (12/51)</t>
+  </si>
+  <si>
+    <t>0.6078 (31/51)</t>
+  </si>
+  <si>
+    <t>0.8039 (41/51)</t>
+  </si>
+  <si>
+    <t>0.8824 (45/51)</t>
+  </si>
+  <si>
+    <t>0.00μm</t>
+  </si>
+  <si>
+    <t>4.83μm</t>
+  </si>
+  <si>
+    <t>3.77μm</t>
+  </si>
+  <si>
+    <t>3.51μm</t>
+  </si>
+  <si>
+    <t>3.62μm</t>
+  </si>
+  <si>
+    <t>53.3s</t>
+  </si>
+  <si>
+    <t>53.7s</t>
+  </si>
+  <si>
+    <t>54.1s</t>
+  </si>
+  <si>
+    <t>53.8s</t>
+  </si>
+  <si>
+    <t>(GT検証: 140)</t>
+  </si>
+  <si>
+    <t>0.1857 (26/140)</t>
+  </si>
+  <si>
+    <t>0.7357 (103/140)</t>
+  </si>
+  <si>
+    <t>0.8786 (123/140)</t>
+  </si>
+  <si>
+    <t>0.8857 (124/140)</t>
+  </si>
+  <si>
+    <t>2.57μm</t>
+  </si>
+  <si>
+    <t>2.28μm</t>
+  </si>
+  <si>
+    <t>2.10μm</t>
+  </si>
+  <si>
+    <t>52.9s</t>
+  </si>
+  <si>
+    <t>53.0s</t>
+  </si>
+  <si>
+    <t>53.1s</t>
+  </si>
+  <si>
+    <t>53.4s</t>
+  </si>
+  <si>
+    <t>(GT検証: 861)</t>
+  </si>
+  <si>
+    <t>0.9222 (794/861)</t>
+  </si>
+  <si>
+    <t>3.55μm</t>
+  </si>
+  <si>
+    <t>55.3s</t>
+  </si>
+  <si>
+    <t>53.9s</t>
+  </si>
+  <si>
+    <t>54.7s</t>
+  </si>
+  <si>
+    <t>(GT検証: 1,198)</t>
+  </si>
+  <si>
+    <t>0.9816 (1,176/1,198)</t>
+  </si>
+  <si>
+    <t>0.9900 (1,186/1,198)</t>
+  </si>
+  <si>
+    <t>0.9908 (1,187/1,198)</t>
+  </si>
+  <si>
+    <t>0.9917 (1,188/1,198)</t>
+  </si>
+  <si>
+    <t>3.33μm</t>
+  </si>
+  <si>
+    <t>3.32μm</t>
+  </si>
+  <si>
+    <t>54.2s</t>
+  </si>
+  <si>
+    <t>55.5s</t>
+  </si>
+  <si>
+    <t>55.4s</t>
+  </si>
+  <si>
+    <t>56.4s</t>
+  </si>
+  <si>
+    <t>44b6_0b24845f</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,8 +419,33 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF101010"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF101010"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF101010"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,8 +458,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -456,11 +697,233 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -540,6 +1003,126 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="19.296875" customWidth="1"/>
@@ -1264,7 +1847,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="10" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>32</v>
@@ -1468,7 +2051,634 @@
         <v>32</v>
       </c>
     </row>
+    <row r="31" spans="2:13">
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="22.8">
+      <c r="B32" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="K32" s="69" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="40">
+        <v>0.12</v>
+      </c>
+      <c r="D33" s="51">
+        <v>1663</v>
+      </c>
+      <c r="E33" s="54">
+        <v>32795</v>
+      </c>
+      <c r="F33" s="41">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G33" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="41">
+        <v>0</v>
+      </c>
+      <c r="I33" s="40">
+        <v>0</v>
+      </c>
+      <c r="J33" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K33" s="42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="31">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D34" s="52">
+        <v>16171</v>
+      </c>
+      <c r="E34" s="55"/>
+      <c r="F34" s="32">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="32">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="I34" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="J34" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34" s="44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="22.8">
+      <c r="B35" s="43"/>
+      <c r="C35" s="33">
+        <v>0.04</v>
+      </c>
+      <c r="D35" s="52">
+        <v>37588</v>
+      </c>
+      <c r="E35" s="55"/>
+      <c r="F35" s="34">
+        <v>1.1459999999999999</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="32">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="I35" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="J35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" s="44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="22.8">
+      <c r="B36" s="43"/>
+      <c r="C36" s="33">
+        <v>0.02</v>
+      </c>
+      <c r="D36" s="52">
+        <v>53871</v>
+      </c>
+      <c r="E36" s="55"/>
+      <c r="F36" s="32">
+        <v>1.643</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" s="32">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="I36" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="J36" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="K36" s="44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="22.8">
+      <c r="B37" s="45"/>
+      <c r="C37" s="35">
+        <v>0.01</v>
+      </c>
+      <c r="D37" s="53">
+        <v>60960</v>
+      </c>
+      <c r="E37" s="56"/>
+      <c r="F37" s="36">
+        <v>1.859</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="36">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="I37" s="37">
+        <v>1E-3</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37" s="46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="22.8">
+      <c r="B38" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="40">
+        <v>0.12</v>
+      </c>
+      <c r="D38" s="51">
+        <v>1389</v>
+      </c>
+      <c r="E38" s="54">
+        <v>15090</v>
+      </c>
+      <c r="F38" s="41">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="G38" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" s="41">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="I38" s="40">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="J38" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="K38" s="42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="22.8">
+      <c r="B39" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="31">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D39" s="52">
+        <v>7428</v>
+      </c>
+      <c r="E39" s="55"/>
+      <c r="F39" s="32">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H39" s="32">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="I39" s="31">
+        <v>2.7E-2</v>
+      </c>
+      <c r="J39" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="K39" s="44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="22.8">
+      <c r="B40" s="43"/>
+      <c r="C40" s="33">
+        <v>0.04</v>
+      </c>
+      <c r="D40" s="52">
+        <v>16040</v>
+      </c>
+      <c r="E40" s="55"/>
+      <c r="F40" s="34">
+        <v>1.0629999999999999</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="32">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="I40" s="31">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J40" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="K40" s="44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="22.8">
+      <c r="B41" s="43"/>
+      <c r="C41" s="31">
+        <v>0.02</v>
+      </c>
+      <c r="D41" s="52">
+        <v>25871</v>
+      </c>
+      <c r="E41" s="55"/>
+      <c r="F41" s="32">
+        <v>1.714</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="H41" s="32">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="I41" s="31">
+        <v>0.01</v>
+      </c>
+      <c r="J41" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41" s="44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="22.8">
+      <c r="B42" s="45"/>
+      <c r="C42" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="D42" s="53">
+        <v>34385</v>
+      </c>
+      <c r="E42" s="56"/>
+      <c r="F42" s="36">
+        <v>2.2789999999999999</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H42" s="36">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="I42" s="37">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="22.8">
+      <c r="B43" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="47">
+        <v>0.12</v>
+      </c>
+      <c r="D43" s="51">
+        <v>7413</v>
+      </c>
+      <c r="E43" s="54">
+        <v>6362</v>
+      </c>
+      <c r="F43" s="48">
+        <v>1.165</v>
+      </c>
+      <c r="G43" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="48">
+        <v>0.1071</v>
+      </c>
+      <c r="I43" s="47">
+        <v>0.192</v>
+      </c>
+      <c r="J43" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="K43" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="22.8">
+      <c r="B44" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="31">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D44" s="52">
+        <v>8763</v>
+      </c>
+      <c r="E44" s="55"/>
+      <c r="F44" s="32">
+        <v>1.377</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H44" s="32">
+        <v>9.06E-2</v>
+      </c>
+      <c r="I44" s="31">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="K44" s="44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="22.8">
+      <c r="B45" s="43"/>
+      <c r="C45" s="31">
+        <v>0.04</v>
+      </c>
+      <c r="D45" s="52">
+        <v>9480</v>
+      </c>
+      <c r="E45" s="55"/>
+      <c r="F45" s="32">
+        <v>1.49</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" s="32">
+        <v>8.3799999999999999E-2</v>
+      </c>
+      <c r="I45" s="31">
+        <v>0.154</v>
+      </c>
+      <c r="J45" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="K45" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" ht="22.8">
+      <c r="B46" s="43"/>
+      <c r="C46" s="31">
+        <v>0.02</v>
+      </c>
+      <c r="D46" s="52">
+        <v>10977</v>
+      </c>
+      <c r="E46" s="55"/>
+      <c r="F46" s="32">
+        <v>1.7250000000000001</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="32">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="I46" s="31">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="J46" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="22.8">
+      <c r="B47" s="45"/>
+      <c r="C47" s="37">
+        <v>0.01</v>
+      </c>
+      <c r="D47" s="53">
+        <v>15309</v>
+      </c>
+      <c r="E47" s="56"/>
+      <c r="F47" s="36">
+        <v>2.4060000000000001</v>
+      </c>
+      <c r="G47" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H47" s="36">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="I47" s="37">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="K47" s="46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="22.8">
+      <c r="B48" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="49">
+        <v>0.12</v>
+      </c>
+      <c r="D48" s="52">
+        <v>9181</v>
+      </c>
+      <c r="E48" s="55">
+        <v>8463</v>
+      </c>
+      <c r="F48" s="58">
+        <v>1.085</v>
+      </c>
+      <c r="G48" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" s="48">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="I48" s="47">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="J48" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="K48" s="44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" ht="22.8">
+      <c r="B49" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="49">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D49" s="52">
+        <v>9750</v>
+      </c>
+      <c r="E49" s="55"/>
+      <c r="F49" s="60">
+        <v>1.1519999999999999</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="H49" s="32">
+        <v>0.1216</v>
+      </c>
+      <c r="I49" s="31">
+        <v>0.217</v>
+      </c>
+      <c r="J49" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="K49" s="44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="22.8">
+      <c r="B50" s="43"/>
+      <c r="C50" s="30">
+        <v>0.04</v>
+      </c>
+      <c r="D50" s="52">
+        <v>10642</v>
+      </c>
+      <c r="E50" s="55"/>
+      <c r="F50" s="60">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="H50" s="32">
+        <v>0.1115</v>
+      </c>
+      <c r="I50" s="31">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="J50" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K50" s="44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="22.8">
+      <c r="B51" s="43"/>
+      <c r="C51" s="30">
+        <v>0.02</v>
+      </c>
+      <c r="D51" s="52">
+        <v>12294</v>
+      </c>
+      <c r="E51" s="55"/>
+      <c r="F51" s="60">
+        <v>1.4530000000000001</v>
+      </c>
+      <c r="G51" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="H51" s="32">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="I51" s="31">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="J51" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K51" s="44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="22.8">
+      <c r="B52" s="45"/>
+      <c r="C52" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="D52" s="53">
+        <v>16555</v>
+      </c>
+      <c r="E52" s="56"/>
+      <c r="F52" s="62">
+        <v>1.956</v>
+      </c>
+      <c r="G52" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52" s="36">
+        <v>7.1800000000000003E-2</v>
+      </c>
+      <c r="I52" s="37">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="J52" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="K52" s="46" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="E38:E42"/>
+    <mergeCell ref="E43:E47"/>
+    <mergeCell ref="E48:E52"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
